--- a/data_fifa.xlsx
+++ b/data_fifa.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/camillepincon/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9185F116-0995-EE4B-AB70-2675495AB6A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB24628B-E461-894E-ABF0-EB93D6FF13DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="260" yWindow="-19700" windowWidth="26440" windowHeight="15160" activeTab="3" xr2:uid="{FE7BC806-2F65-C14F-9217-93106962ADF2}"/>
+    <workbookView xWindow="260" yWindow="-19700" windowWidth="26440" windowHeight="15160" activeTab="2" xr2:uid="{FE7BC806-2F65-C14F-9217-93106962ADF2}"/>
   </bookViews>
   <sheets>
     <sheet name="stadiums" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,9 @@
     <sheet name="teams" sheetId="5" r:id="rId4"/>
     <sheet name="teams-camps" sheetId="4" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">camps!$A$1:$F$1</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -43,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1780" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1888" uniqueCount="535">
   <si>
     <t>UTC_Offset</t>
   </si>
@@ -859,9 +862,6 @@
   </si>
   <si>
     <t>-79.9620</t>
-  </si>
-  <si>
-    <t>Houston Sports Park</t>
   </si>
   <si>
     <t>Omni Houston Hotel</t>
@@ -1685,15 +1685,33 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1712,22 +1730,60 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1741,8 +1797,35 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E62EFE71-D0B5-8B4C-B469-AD51C65C78E2}" name="Tableau4" displayName="Tableau4" ref="A1:K17" totalsRowShown="0">
+  <autoFilter ref="A1:K17" xr:uid="{E62EFE71-D0B5-8B4C-B469-AD51C65C78E2}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{2C23BCF2-79AB-C248-85F4-AB2BBC901CE4}" name="city"/>
+    <tableColumn id="2" xr3:uid="{A4376D2F-AF9F-3B4F-986A-59DAF56666F3}" name="stadium"/>
+    <tableColumn id="3" xr3:uid="{E56042F1-B611-8848-B275-8A3E86BF5EDD}" name="country"/>
+    <tableColumn id="4" xr3:uid="{B56C129B-9D7C-2248-894B-D1943B83419F}" name="let"/>
+    <tableColumn id="5" xr3:uid="{21CA2182-D90E-8D42-83B7-74413F879C76}" name="long"/>
+    <tableColumn id="6" xr3:uid="{52696AFB-2559-A142-83C5-0495ADEB5B77}" name="alt_m"/>
+    <tableColumn id="7" xr3:uid="{BF86AEC9-7D9C-2148-A6B8-A44DEFD5FF47}" name="capacity"/>
+    <tableColumn id="8" xr3:uid="{E1A0ACB9-D698-5549-8373-81014E25CDD5}" name="temp_C_june"/>
+    <tableColumn id="9" xr3:uid="{99B02484-6E15-3948-8261-3E424615AD9A}" name="humidity_%_june"/>
+    <tableColumn id="10" xr3:uid="{00DF30E5-F593-E141-84C3-E3B4E0109CC1}" name="time_zone"/>
+    <tableColumn id="11" xr3:uid="{13DD253E-0FCC-A64A-AB44-CC990A10D50E}" name="UTC_Offset"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{59DEFAEC-8FFE-DD4F-BA51-16EAB1F37A3E}" name="Tableau1" displayName="Tableau1" ref="A1:K73" totalsRowShown="0">
-  <autoFilter ref="A1:K73" xr:uid="{59DEFAEC-8FFE-DD4F-BA51-16EAB1F37A3E}"/>
+  <autoFilter ref="A1:K73" xr:uid="{59DEFAEC-8FFE-DD4F-BA51-16EAB1F37A3E}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="Iran"/>
+        <filter val="Iraq"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K73">
     <sortCondition ref="G1:G73"/>
   </sortState>
@@ -1763,7 +1846,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2E1A9C9D-2528-4543-A552-A9452530CBD1}" name="Tableau3" displayName="Tableau3" ref="A1:N49" totalsRowShown="0">
   <autoFilter ref="A1:N49" xr:uid="{2E1A9C9D-2528-4543-A552-A9452530CBD1}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I49">
@@ -1789,7 +1872,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{AE02F85E-BEBE-5F4D-BBF5-D66371D919EE}" name="Tableau2" displayName="Tableau2" ref="A1:F49" totalsRowShown="0">
   <autoFilter ref="A1:F49" xr:uid="{AE02F85E-BEBE-5F4D-BBF5-D66371D919EE}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F49">
@@ -2132,6 +2215,10 @@
     <col min="3" max="3" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.33203125" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="12" width="43.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2780,6 +2867,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -2827,7 +2917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>25</v>
       </c>
@@ -2862,7 +2952,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2897,7 +2987,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>52</v>
       </c>
@@ -2932,7 +3022,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>28</v>
       </c>
@@ -2967,7 +3057,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>13</v>
       </c>
@@ -3002,7 +3092,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>54</v>
       </c>
@@ -3037,7 +3127,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>37</v>
       </c>
@@ -3072,7 +3162,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>5</v>
       </c>
@@ -3107,7 +3197,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>70</v>
       </c>
@@ -3142,7 +3232,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>27</v>
       </c>
@@ -3177,7 +3267,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>49</v>
       </c>
@@ -3212,7 +3302,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>7</v>
       </c>
@@ -3247,7 +3337,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>29</v>
       </c>
@@ -3317,7 +3407,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>61</v>
       </c>
@@ -3352,7 +3442,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>46</v>
       </c>
@@ -3387,7 +3477,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>10</v>
       </c>
@@ -3422,7 +3512,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>57</v>
       </c>
@@ -3457,7 +3547,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>41</v>
       </c>
@@ -3492,7 +3582,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>8</v>
       </c>
@@ -3527,7 +3617,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>72</v>
       </c>
@@ -3562,7 +3652,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>32</v>
       </c>
@@ -3597,7 +3687,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>22</v>
       </c>
@@ -3632,7 +3722,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>60</v>
       </c>
@@ -3667,7 +3757,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>9</v>
       </c>
@@ -3702,7 +3792,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>33</v>
       </c>
@@ -3737,7 +3827,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>63</v>
       </c>
@@ -3772,7 +3862,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>21</v>
       </c>
@@ -3807,7 +3897,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>45</v>
       </c>
@@ -3842,7 +3932,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>35</v>
       </c>
@@ -3877,7 +3967,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>58</v>
       </c>
@@ -3912,7 +4002,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>12</v>
       </c>
@@ -3947,7 +4037,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>19</v>
       </c>
@@ -3982,7 +4072,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>36</v>
       </c>
@@ -4017,7 +4107,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>71</v>
       </c>
@@ -4052,7 +4142,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>26</v>
       </c>
@@ -4087,7 +4177,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>14</v>
       </c>
@@ -4122,7 +4212,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>4</v>
       </c>
@@ -4157,7 +4247,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>59</v>
       </c>
@@ -4192,7 +4282,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4262,7 +4352,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>66</v>
       </c>
@@ -4297,7 +4387,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>38</v>
       </c>
@@ -4332,7 +4422,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>1</v>
       </c>
@@ -4367,7 +4457,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>53</v>
       </c>
@@ -4402,7 +4492,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>24</v>
       </c>
@@ -4437,7 +4527,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>51</v>
       </c>
@@ -4472,7 +4562,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>64</v>
       </c>
@@ -4507,7 +4597,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>15</v>
       </c>
@@ -4542,7 +4632,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>39</v>
       </c>
@@ -4577,7 +4667,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>69</v>
       </c>
@@ -4612,7 +4702,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>6</v>
       </c>
@@ -4647,7 +4737,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>55</v>
       </c>
@@ -4682,7 +4772,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>17</v>
       </c>
@@ -4717,7 +4807,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>43</v>
       </c>
@@ -4752,7 +4842,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>20</v>
       </c>
@@ -4787,7 +4877,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>67</v>
       </c>
@@ -4822,7 +4912,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>44</v>
       </c>
@@ -4857,7 +4947,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>31</v>
       </c>
@@ -4892,7 +4982,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>11</v>
       </c>
@@ -4927,7 +5017,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>56</v>
       </c>
@@ -4962,7 +5052,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>42</v>
       </c>
@@ -4997,7 +5087,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>68</v>
       </c>
@@ -5032,7 +5122,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>48</v>
       </c>
@@ -5067,7 +5157,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>50</v>
       </c>
@@ -5102,7 +5192,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>30</v>
       </c>
@@ -5137,7 +5227,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>65</v>
       </c>
@@ -5172,7 +5262,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>3</v>
       </c>
@@ -5207,7 +5297,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>34</v>
       </c>
@@ -5242,7 +5332,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>62</v>
       </c>
@@ -5277,7 +5367,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>23</v>
       </c>
@@ -5312,7 +5402,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>47</v>
       </c>
@@ -5357,8 +5447,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F12EB328-9F28-E94D-A90D-83809AACB74A}">
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="47.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
@@ -5382,1245 +5475,1613 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>155</v>
+        <v>321</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>154</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>156</v>
+        <v>322</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>157</v>
+        <v>323</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>158</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>159</v>
+        <v>317</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>160</v>
+        <v>318</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>161</v>
+        <v>319</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>162</v>
+        <v>320</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>13</v>
+        <v>358</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>164</v>
+        <v>364</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>166</v>
+        <v>366</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>168</v>
+        <v>359</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>167</v>
+        <v>358</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>169</v>
+        <v>360</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>170</v>
+        <v>361</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>171</v>
+        <v>362</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>173</v>
+        <v>254</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>172</v>
+        <v>5</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>174</v>
+        <v>255</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>175</v>
+        <v>256</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>176</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>178</v>
+        <v>387</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>177</v>
+        <v>386</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>179</v>
+        <v>388</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>180</v>
+        <v>389</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>181</v>
+        <v>390</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>183</v>
+        <v>258</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>182</v>
+        <v>5</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>184</v>
+        <v>259</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>185</v>
+        <v>260</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>186</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>9</v>
+      <c r="A9" s="13" t="s">
+        <v>508</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>507</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>2</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>191</v>
+        <v>403</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>193</v>
+        <v>434</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>192</v>
+        <v>433</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>194</v>
+        <v>435</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>195</v>
+        <v>436</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>196</v>
+        <v>437</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>9</v>
+      <c r="A11" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>2</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>201</v>
+        <v>326</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>202</v>
+        <v>172</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>204</v>
+        <v>174</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>205</v>
+        <v>175</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>206</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>208</v>
+        <v>368</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>207</v>
+        <v>367</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>209</v>
+        <v>369</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>210</v>
+        <v>370</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>211</v>
+        <v>371</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="A14" s="18" t="s">
+        <v>382</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="C14" s="18" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>215</v>
+        <v>383</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>384</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="3" t="s">
+      <c r="A15" s="18" t="s">
+        <v>429</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>428</v>
+      </c>
+      <c r="C15" s="18" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>219</v>
+        <v>430</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>431</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="A16" s="18" t="s">
+        <v>354</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>353</v>
+      </c>
+      <c r="C16" s="18" t="s">
         <v>9</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>223</v>
+        <v>355</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>356</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="A17" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>396</v>
+      </c>
+      <c r="C17" s="18" t="s">
         <v>9</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>228</v>
+        <v>398</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>399</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
-        <v>230</v>
+      <c r="A18" s="13" t="s">
+        <v>470</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>229</v>
+        <v>8</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>231</v>
+        <v>272</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>232</v>
+        <v>273</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="A19" s="11" t="s">
+        <v>451</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>450</v>
+      </c>
+      <c r="C19" s="14" t="s">
         <v>9</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>238</v>
+        <v>403</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>452</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>240</v>
+        <v>439</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>239</v>
+        <v>438</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>241</v>
+        <v>440</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>242</v>
+        <v>441</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>243</v>
+        <v>442</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>9</v>
+      <c r="A21" s="13" t="s">
+        <v>483</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>482</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>2</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>248</v>
+        <v>403</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>484</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>254</v>
+        <v>212</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>255</v>
+        <v>213</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>256</v>
+        <v>214</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>257</v>
+        <v>215</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>2</v>
+      <c r="A24" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>9</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>261</v>
+        <v>231</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="C25" s="3" t="s">
+      <c r="A25" s="11" t="s">
+        <v>494</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>493</v>
+      </c>
+      <c r="C25" s="14" t="s">
         <v>9</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>266</v>
+        <v>403</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>495</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>268</v>
+        <v>303</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>267</v>
+        <v>302</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>270</v>
+        <v>305</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>271</v>
+        <v>306</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="3" t="s">
+      <c r="A27" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="18" t="s">
         <v>9</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>275</v>
+        <v>221</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="F27" s="18" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="C28" s="3" t="s">
+      <c r="A28" s="11" t="s">
+        <v>504</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>493</v>
+      </c>
+      <c r="C28" s="14" t="s">
         <v>9</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>280</v>
+        <v>403</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>505</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>282</v>
+        <v>216</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>281</v>
+        <v>11</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>283</v>
+        <v>217</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>284</v>
+        <v>218</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>285</v>
+        <v>219</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30" s="3" t="s">
+      <c r="A30" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="C30" s="18" t="s">
         <v>9</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>289</v>
+        <v>226</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="F30" s="18" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>12</v>
+        <v>307</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>294</v>
+        <v>168</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>12</v>
+        <v>167</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>295</v>
+        <v>169</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>296</v>
+        <v>170</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>297</v>
+        <v>171</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>299</v>
+        <v>281</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>304</v>
+        <v>330</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>303</v>
+        <v>329</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>305</v>
+        <v>331</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>307</v>
+        <v>333</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>309</v>
+        <v>159</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>308</v>
+        <v>13</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>310</v>
+        <v>160</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>311</v>
+        <v>161</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>312</v>
+        <v>162</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A36" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="C36" s="3" t="s">
+      <c r="A36" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="C36" s="18" t="s">
         <v>9</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>317</v>
+        <v>204</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="F36" s="18" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>318</v>
+        <v>163</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>319</v>
+        <v>164</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>320</v>
+        <v>165</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>321</v>
+        <v>166</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A38" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>2</v>
+      <c r="A38" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>401</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>9</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>325</v>
+        <v>403</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="F38" s="18" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A39" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>2</v>
+      <c r="A39" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>401</v>
+      </c>
+      <c r="C39" s="18" t="s">
+        <v>9</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>329</v>
+        <v>403</v>
+      </c>
+      <c r="E39" s="18" t="s">
+        <v>407</v>
+      </c>
+      <c r="F39" s="18" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>331</v>
+        <v>188</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>330</v>
+        <v>187</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>332</v>
+        <v>189</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>333</v>
+        <v>190</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>334</v>
+        <v>191</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A41" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="C41" s="3" t="s">
+      <c r="A41" s="18" t="s">
+        <v>349</v>
+      </c>
+      <c r="B41" s="19" t="s">
+        <v>344</v>
+      </c>
+      <c r="C41" s="18" t="s">
         <v>9</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>339</v>
+        <v>350</v>
+      </c>
+      <c r="E41" s="18" t="s">
+        <v>351</v>
+      </c>
+      <c r="F41" s="18" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A42" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="C42" s="3" t="s">
+      <c r="A42" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="B42" s="16" t="s">
+        <v>472</v>
+      </c>
+      <c r="C42" s="16" t="s">
         <v>9</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="F42" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>474</v>
+      </c>
+      <c r="F42" s="16" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A43" s="18" t="s">
+        <v>345</v>
+      </c>
+      <c r="B43" s="19" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A43" s="3" t="s">
+      <c r="C43" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="3" t="s">
+      <c r="E43" s="18" t="s">
         <v>347</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="F43" s="18" t="s">
         <v>348</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>349</v>
-      </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A44" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C44" s="3" t="s">
+      <c r="A44" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="B44" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="C44" s="18" t="s">
         <v>9</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>353</v>
+        <v>184</v>
+      </c>
+      <c r="E44" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="F44" s="18" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>355</v>
+        <v>268</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>354</v>
+        <v>267</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>356</v>
+        <v>269</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>357</v>
+        <v>270</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>358</v>
+        <v>271</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>2</v>
+      <c r="A46" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="B46" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="C46" s="18" t="s">
+        <v>9</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>363</v>
+        <v>251</v>
+      </c>
+      <c r="E46" s="18" t="s">
+        <v>252</v>
+      </c>
+      <c r="F46" s="18" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A47" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>2</v>
+      <c r="A47" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>9</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>367</v>
+        <v>403</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>489</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A48" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="C48" s="3" t="s">
+      <c r="A48" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="C48" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="F48" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A49" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A50" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A51" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="F51" s="17" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A52" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="B52" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="F52" s="17" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A53" s="12" t="s">
+        <v>420</v>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>419</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="E53" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="F53" s="17" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A54" s="12" t="s">
+        <v>424</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>419</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="E54" s="12" t="s">
+        <v>426</v>
+      </c>
+      <c r="F54" s="17" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A55" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E55" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="F55" s="17" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A56" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="B56" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="E56" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="F56" s="17" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A57" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="B57" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="E57" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="F57" s="17" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A58" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="B58" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E58" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="F58" s="17" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A59" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A60" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="B60" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="F60" s="17" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A61" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="B61" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="F61" s="17" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A62" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="B62" s="15" t="s">
+        <v>339</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="E62" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="F62" s="17" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A63" s="12" t="s">
         <v>372</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A49" s="3" t="s">
+      <c r="B63" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D63" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="3" t="s">
+      <c r="E63" s="12" t="s">
         <v>374</v>
       </c>
-      <c r="E49" s="3" t="s">
+      <c r="F63" s="17" t="s">
         <v>375</v>
       </c>
-      <c r="F49" s="3" t="s">
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A64" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="B64" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E64" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="F64" s="17" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A65" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="B65" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="E65" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="F65" s="17" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A66" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="B66" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E66" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="F66" s="17" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A67" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="B67" s="15" t="s">
+        <v>334</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="E67" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="F67" s="17" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A68" s="10" t="s">
+        <v>461</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A69" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A70" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A71" s="12" t="s">
+        <v>410</v>
+      </c>
+      <c r="B71" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="E71" s="12" t="s">
+        <v>412</v>
+      </c>
+      <c r="F71" s="17" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A72" s="10" t="s">
+        <v>479</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D72" t="s">
+        <v>403</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A73" s="10" t="s">
+        <v>476</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D73" t="s">
+        <v>403</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A74" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="B74" s="15" t="s">
+        <v>312</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="E74" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="F74" s="17" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A75" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B75" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="E75" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="F75" s="17" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A76" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="B76" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E76" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="F76" s="17" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A77" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>497</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="F77" s="7" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A78" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="B78" s="15" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A50" s="3" t="s">
+      <c r="C78" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D78" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" s="3" t="s">
+      <c r="E78" s="12" t="s">
         <v>379</v>
       </c>
-      <c r="E50" s="3" t="s">
+      <c r="F78" s="17" t="s">
         <v>380</v>
       </c>
-      <c r="F50" s="3" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A51" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A52" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="F52" s="3" t="s">
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A79" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="B79" s="15" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A53" s="3" t="s">
+      <c r="C79" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D79" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D53" s="3" t="s">
+      <c r="E79" s="12" t="s">
         <v>394</v>
       </c>
-      <c r="E53" s="3" t="s">
+      <c r="F79" s="17" t="s">
         <v>395</v>
       </c>
-      <c r="F53" s="3" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A54" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A55" s="3" t="s">
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A80" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="B80" s="15" t="s">
+        <v>414</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="E80" s="12" t="s">
+        <v>417</v>
+      </c>
+      <c r="F80" s="17" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A81" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D81" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A56" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A57" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A58" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A59" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A60" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A61" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A62" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A63" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>443</v>
+      <c r="E81" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>469</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F1" xr:uid="{F12EB328-9F28-E94D-A90D-83809AACB74A}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F81">
+      <sortCondition ref="E1:E81"/>
+    </sortState>
+  </autoFilter>
+  <conditionalFormatting sqref="E1:E1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6640,46 +7101,46 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B1" t="s">
         <v>142</v>
       </c>
       <c r="C1" t="s">
+        <v>523</v>
+      </c>
+      <c r="D1" t="s">
         <v>524</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>525</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>526</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>527</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>528</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>529</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>530</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>531</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>532</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>533</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>534</v>
-      </c>
-      <c r="N1" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
@@ -6696,7 +7157,7 @@
         <v>1564.26</v>
       </c>
       <c r="E2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F2">
         <v>36.74</v>
@@ -6708,7 +7169,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J2" t="s">
         <v>12</v>
@@ -6717,13 +7178,13 @@
         <v>9</v>
       </c>
       <c r="L2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M2" t="s">
+        <v>295</v>
+      </c>
+      <c r="N2" t="s">
         <v>296</v>
-      </c>
-      <c r="N2" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
@@ -6740,7 +7201,7 @@
         <v>1874.81</v>
       </c>
       <c r="E3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F3">
         <v>-34.61</v>
@@ -6752,7 +7213,7 @@
         <v>-3</v>
       </c>
       <c r="I3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="J3" t="s">
         <v>12</v>
@@ -6761,13 +7222,13 @@
         <v>9</v>
       </c>
       <c r="L3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="M3" t="s">
+        <v>291</v>
+      </c>
+      <c r="N3" t="s">
         <v>292</v>
-      </c>
-      <c r="N3" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -6784,7 +7245,7 @@
         <v>1580.67</v>
       </c>
       <c r="E4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F4">
         <v>-35.28</v>
@@ -6796,22 +7257,22 @@
         <v>10</v>
       </c>
       <c r="I4" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="J4" t="s">
+        <v>454</v>
+      </c>
+      <c r="K4" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" t="s">
         <v>455</v>
       </c>
-      <c r="K4" t="s">
-        <v>9</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>456</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>457</v>
-      </c>
-      <c r="N4" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -6828,7 +7289,7 @@
         <v>1593.45</v>
       </c>
       <c r="E5" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F5">
         <v>48.21</v>
@@ -6840,22 +7301,22 @@
         <v>2</v>
       </c>
       <c r="I5" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="J5" t="s">
+        <v>458</v>
+      </c>
+      <c r="K5" t="s">
+        <v>9</v>
+      </c>
+      <c r="L5" t="s">
         <v>459</v>
       </c>
-      <c r="K5" t="s">
-        <v>9</v>
-      </c>
-      <c r="L5" t="s">
-        <v>460</v>
-      </c>
       <c r="M5" t="s">
+        <v>404</v>
+      </c>
+      <c r="N5" t="s">
         <v>405</v>
-      </c>
-      <c r="N5" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -6872,7 +7333,7 @@
         <v>1734.71</v>
       </c>
       <c r="E6" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F6">
         <v>50.85</v>
@@ -6884,22 +7345,22 @@
         <v>2</v>
       </c>
       <c r="I6" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="J6" t="s">
+        <v>391</v>
+      </c>
+      <c r="K6" t="s">
+        <v>9</v>
+      </c>
+      <c r="L6" t="s">
         <v>392</v>
       </c>
-      <c r="K6" t="s">
-        <v>9</v>
-      </c>
-      <c r="L6" t="s">
-        <v>393</v>
-      </c>
       <c r="M6" t="s">
+        <v>394</v>
+      </c>
+      <c r="N6" t="s">
         <v>395</v>
-      </c>
-      <c r="N6" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -6916,7 +7377,7 @@
         <v>1385.84</v>
       </c>
       <c r="E7" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F7">
         <v>43.85</v>
@@ -6928,22 +7389,22 @@
         <v>2</v>
       </c>
       <c r="I7" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="J7" t="s">
+        <v>460</v>
+      </c>
+      <c r="K7" t="s">
+        <v>9</v>
+      </c>
+      <c r="L7" t="s">
         <v>461</v>
       </c>
-      <c r="K7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L7" t="s">
+      <c r="M7" t="s">
         <v>462</v>
       </c>
-      <c r="M7" t="s">
+      <c r="N7" t="s">
         <v>463</v>
-      </c>
-      <c r="N7" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -6960,7 +7421,7 @@
         <v>1761.16</v>
       </c>
       <c r="E8" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F8">
         <v>-15.78</v>
@@ -6972,22 +7433,22 @@
         <v>-3</v>
       </c>
       <c r="I8" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="J8" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="K8" t="s">
         <v>9</v>
       </c>
       <c r="L8" t="s">
+        <v>464</v>
+      </c>
+      <c r="M8" t="s">
         <v>465</v>
       </c>
-      <c r="M8" t="s">
+      <c r="N8" t="s">
         <v>466</v>
-      </c>
-      <c r="N8" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -7004,7 +7465,7 @@
         <v>1556.48</v>
       </c>
       <c r="E9" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F9">
         <v>45.42</v>
@@ -7016,7 +7477,7 @@
         <v>-4</v>
       </c>
       <c r="I9" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="J9" t="s">
         <v>28</v>
@@ -7025,13 +7486,13 @@
         <v>25</v>
       </c>
       <c r="L9" t="s">
+        <v>467</v>
+      </c>
+      <c r="M9" t="s">
         <v>468</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>469</v>
-      </c>
-      <c r="N9" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -7048,7 +7509,7 @@
         <v>1366.13</v>
       </c>
       <c r="E10" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F10">
         <v>14.93</v>
@@ -7060,22 +7521,22 @@
         <v>-1</v>
       </c>
       <c r="I10" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J10" t="s">
+        <v>428</v>
+      </c>
+      <c r="K10" t="s">
+        <v>9</v>
+      </c>
+      <c r="L10" t="s">
         <v>429</v>
       </c>
-      <c r="K10" t="s">
-        <v>9</v>
-      </c>
-      <c r="L10" t="s">
-        <v>430</v>
-      </c>
       <c r="M10" t="s">
+        <v>431</v>
+      </c>
+      <c r="N10" t="s">
         <v>432</v>
-      </c>
-      <c r="N10" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -7092,7 +7553,7 @@
         <v>1693.09</v>
       </c>
       <c r="E11" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F11">
         <v>4.71</v>
@@ -7104,7 +7565,7 @@
         <v>-5</v>
       </c>
       <c r="I11" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="J11" t="s">
         <v>5</v>
@@ -7136,7 +7597,7 @@
         <v>1717.07</v>
       </c>
       <c r="E12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F12">
         <v>45.81</v>
@@ -7148,7 +7609,7 @@
         <v>2</v>
       </c>
       <c r="I12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="J12" t="s">
         <v>154</v>
@@ -7180,7 +7641,7 @@
         <v>1294.6500000000001</v>
       </c>
       <c r="E13" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F13">
         <v>12.11</v>
@@ -7192,7 +7653,7 @@
         <v>-4</v>
       </c>
       <c r="I13" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="J13" t="s">
         <v>172</v>
@@ -7224,7 +7685,7 @@
         <v>1501.38</v>
       </c>
       <c r="E14" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F14">
         <v>50.08</v>
@@ -7236,7 +7697,7 @@
         <v>2</v>
       </c>
       <c r="I14" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="J14" t="s">
         <v>11</v>
@@ -7268,7 +7729,7 @@
         <v>1478.35</v>
       </c>
       <c r="E15" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F15">
         <v>-4.32</v>
@@ -7280,7 +7741,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J15" t="s">
         <v>8</v>
@@ -7289,13 +7750,13 @@
         <v>9</v>
       </c>
       <c r="L15" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="M15" t="s">
+        <v>273</v>
+      </c>
+      <c r="N15" t="s">
         <v>274</v>
-      </c>
-      <c r="N15" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
@@ -7312,7 +7773,7 @@
         <v>1594.78</v>
       </c>
       <c r="E16" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F16">
         <v>-0.22</v>
@@ -7324,7 +7785,7 @@
         <v>-5</v>
       </c>
       <c r="I16" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="J16" t="s">
         <v>207</v>
@@ -7356,7 +7817,7 @@
         <v>1563.24</v>
       </c>
       <c r="E17" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F17">
         <v>30.04</v>
@@ -7368,22 +7829,22 @@
         <v>2</v>
       </c>
       <c r="I17" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J17" t="s">
+        <v>414</v>
+      </c>
+      <c r="K17" t="s">
+        <v>9</v>
+      </c>
+      <c r="L17" t="s">
         <v>415</v>
       </c>
-      <c r="K17" t="s">
-        <v>9</v>
-      </c>
-      <c r="L17" t="s">
-        <v>416</v>
-      </c>
       <c r="M17" t="s">
+        <v>417</v>
+      </c>
+      <c r="N17" t="s">
         <v>418</v>
-      </c>
-      <c r="N17" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
@@ -7400,7 +7861,7 @@
         <v>1825.97</v>
       </c>
       <c r="E18" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F18">
         <v>51.51</v>
@@ -7412,7 +7873,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="J18" t="s">
         <v>12</v>
@@ -7421,13 +7882,13 @@
         <v>9</v>
       </c>
       <c r="L18" t="s">
+        <v>447</v>
+      </c>
+      <c r="M18" t="s">
         <v>448</v>
       </c>
-      <c r="M18" t="s">
+      <c r="N18" t="s">
         <v>449</v>
-      </c>
-      <c r="N18" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
@@ -7444,7 +7905,7 @@
         <v>1877.32</v>
       </c>
       <c r="E19" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F19">
         <v>48.86</v>
@@ -7456,7 +7917,7 @@
         <v>2</v>
       </c>
       <c r="I19" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="J19" t="s">
         <v>22</v>
@@ -7465,13 +7926,13 @@
         <v>9</v>
       </c>
       <c r="L19" t="s">
+        <v>476</v>
+      </c>
+      <c r="M19" t="s">
         <v>477</v>
       </c>
-      <c r="M19" t="s">
+      <c r="N19" t="s">
         <v>478</v>
-      </c>
-      <c r="N19" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
@@ -7488,7 +7949,7 @@
         <v>1730.37</v>
       </c>
       <c r="E20" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F20">
         <v>52.52</v>
@@ -7500,22 +7961,22 @@
         <v>2</v>
       </c>
       <c r="I20" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="J20" t="s">
+        <v>443</v>
+      </c>
+      <c r="K20" t="s">
+        <v>9</v>
+      </c>
+      <c r="L20" t="s">
         <v>444</v>
       </c>
-      <c r="K20" t="s">
-        <v>9</v>
-      </c>
-      <c r="L20" t="s">
+      <c r="M20" t="s">
         <v>445</v>
       </c>
-      <c r="M20" t="s">
+      <c r="N20" t="s">
         <v>446</v>
-      </c>
-      <c r="N20" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
@@ -7532,7 +7993,7 @@
         <v>1346.31</v>
       </c>
       <c r="E21" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F21">
         <v>5.56</v>
@@ -7544,7 +8005,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J21" t="s">
         <v>22</v>
@@ -7553,13 +8014,13 @@
         <v>9</v>
       </c>
       <c r="L21" t="s">
+        <v>479</v>
+      </c>
+      <c r="M21" t="s">
         <v>480</v>
       </c>
-      <c r="M21" t="s">
+      <c r="N21" t="s">
         <v>481</v>
-      </c>
-      <c r="N21" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
@@ -7576,7 +8037,7 @@
         <v>1291.71</v>
       </c>
       <c r="E22" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F22">
         <v>18.54</v>
@@ -7588,22 +8049,22 @@
         <v>-4</v>
       </c>
       <c r="I22" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="J22" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="K22" t="s">
         <v>9</v>
       </c>
       <c r="L22" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="M22" t="s">
+        <v>342</v>
+      </c>
+      <c r="N22" t="s">
         <v>343</v>
-      </c>
-      <c r="N22" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
@@ -7620,7 +8081,7 @@
         <v>1615.3</v>
       </c>
       <c r="E23" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F23">
         <v>35.69</v>
@@ -7632,22 +8093,22 @@
         <v>3</v>
       </c>
       <c r="I23" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J23" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="K23" t="s">
         <v>2</v>
       </c>
       <c r="L23" t="s">
+        <v>483</v>
+      </c>
+      <c r="M23" t="s">
         <v>484</v>
       </c>
-      <c r="M23" t="s">
+      <c r="N23" t="s">
         <v>485</v>
-      </c>
-      <c r="N23" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
@@ -7664,7 +8125,7 @@
         <v>1447.14</v>
       </c>
       <c r="E24" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F24">
         <v>33.340000000000003</v>
@@ -7676,7 +8137,7 @@
         <v>3</v>
       </c>
       <c r="I24" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J24" t="s">
         <v>244</v>
@@ -7708,7 +8169,7 @@
         <v>1532.98</v>
       </c>
       <c r="E25" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F25">
         <v>6.82</v>
@@ -7720,22 +8181,22 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J25" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="K25" t="s">
         <v>9</v>
       </c>
       <c r="L25" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="M25" t="s">
+        <v>374</v>
+      </c>
+      <c r="N25" t="s">
         <v>375</v>
-      </c>
-      <c r="N25" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
@@ -7752,7 +8213,7 @@
         <v>1660.43</v>
       </c>
       <c r="E26" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F26">
         <v>35.69</v>
@@ -7764,22 +8225,22 @@
         <v>9</v>
       </c>
       <c r="I26" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J26" t="s">
+        <v>486</v>
+      </c>
+      <c r="K26" t="s">
+        <v>9</v>
+      </c>
+      <c r="L26" t="s">
         <v>487</v>
       </c>
-      <c r="K26" t="s">
-        <v>9</v>
-      </c>
-      <c r="L26" t="s">
+      <c r="M26" t="s">
         <v>488</v>
       </c>
-      <c r="M26" t="s">
+      <c r="N26" t="s">
         <v>489</v>
-      </c>
-      <c r="N26" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
@@ -7796,7 +8257,7 @@
         <v>1391.45</v>
       </c>
       <c r="E27" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F27">
         <v>31.96</v>
@@ -7808,22 +8269,22 @@
         <v>3</v>
       </c>
       <c r="I27" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J27" t="s">
+        <v>376</v>
+      </c>
+      <c r="K27" t="s">
+        <v>9</v>
+      </c>
+      <c r="L27" t="s">
         <v>377</v>
       </c>
-      <c r="K27" t="s">
-        <v>9</v>
-      </c>
-      <c r="L27" t="s">
-        <v>378</v>
-      </c>
       <c r="M27" t="s">
+        <v>379</v>
+      </c>
+      <c r="N27" t="s">
         <v>380</v>
-      </c>
-      <c r="N27" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
@@ -7840,7 +8301,7 @@
         <v>1588.66</v>
       </c>
       <c r="E28" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F28">
         <v>37.57</v>
@@ -7852,7 +8313,7 @@
         <v>9</v>
       </c>
       <c r="I28" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J28" t="s">
         <v>5</v>
@@ -7884,7 +8345,7 @@
         <v>1681.03</v>
       </c>
       <c r="E29" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F29">
         <v>19.43</v>
@@ -7896,7 +8357,7 @@
         <v>-6</v>
       </c>
       <c r="I29" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="J29" t="s">
         <v>1</v>
@@ -7905,13 +8366,13 @@
         <v>2</v>
       </c>
       <c r="L29" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="M29" t="s">
+        <v>319</v>
+      </c>
+      <c r="N29" t="s">
         <v>320</v>
-      </c>
-      <c r="N29" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
@@ -7928,7 +8389,7 @@
         <v>1755.87</v>
       </c>
       <c r="E30" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F30">
         <v>34.020000000000003</v>
@@ -7940,22 +8401,22 @@
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J30" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="K30" t="s">
         <v>9</v>
       </c>
       <c r="L30" t="s">
+        <v>490</v>
+      </c>
+      <c r="M30" t="s">
         <v>491</v>
       </c>
-      <c r="M30" t="s">
+      <c r="N30" t="s">
         <v>492</v>
-      </c>
-      <c r="N30" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
@@ -7972,7 +8433,7 @@
         <v>1757.87</v>
       </c>
       <c r="E31" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F31">
         <v>52.37</v>
@@ -7984,7 +8445,7 @@
         <v>2</v>
       </c>
       <c r="I31" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="J31" t="s">
         <v>12</v>
@@ -7993,13 +8454,13 @@
         <v>9</v>
       </c>
       <c r="L31" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="M31" t="s">
+        <v>287</v>
+      </c>
+      <c r="N31" t="s">
         <v>288</v>
-      </c>
-      <c r="N31" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
@@ -8016,7 +8477,7 @@
         <v>1281.57</v>
       </c>
       <c r="E32" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F32">
         <v>-41.29</v>
@@ -8028,22 +8489,22 @@
         <v>12</v>
       </c>
       <c r="I32" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="J32" t="s">
+        <v>493</v>
+      </c>
+      <c r="K32" t="s">
+        <v>9</v>
+      </c>
+      <c r="L32" t="s">
         <v>494</v>
       </c>
-      <c r="K32" t="s">
-        <v>9</v>
-      </c>
-      <c r="L32" t="s">
+      <c r="M32" t="s">
         <v>495</v>
       </c>
-      <c r="M32" t="s">
+      <c r="N32" t="s">
         <v>496</v>
-      </c>
-      <c r="N32" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
@@ -8060,7 +8521,7 @@
         <v>1550.94</v>
       </c>
       <c r="E33" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F33">
         <v>59.91</v>
@@ -8072,7 +8533,7 @@
         <v>2</v>
       </c>
       <c r="I33" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="J33" t="s">
         <v>249</v>
@@ -8104,7 +8565,7 @@
         <v>1540.64</v>
       </c>
       <c r="E34" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F34">
         <v>8.99</v>
@@ -8116,22 +8577,22 @@
         <v>-5</v>
       </c>
       <c r="I34" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="J34" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K34" t="s">
         <v>25</v>
       </c>
       <c r="L34" t="s">
+        <v>498</v>
+      </c>
+      <c r="M34" t="s">
         <v>499</v>
       </c>
-      <c r="M34" t="s">
+      <c r="N34" t="s">
         <v>500</v>
-      </c>
-      <c r="N34" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
@@ -8148,7 +8609,7 @@
         <v>1503.5</v>
       </c>
       <c r="E35" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F35">
         <v>-25.28</v>
@@ -8160,22 +8621,22 @@
         <v>-4</v>
       </c>
       <c r="I35" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="J35" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K35" t="s">
         <v>9</v>
       </c>
       <c r="L35" t="s">
+        <v>501</v>
+      </c>
+      <c r="M35" t="s">
         <v>502</v>
       </c>
-      <c r="M35" t="s">
+      <c r="N35" t="s">
         <v>503</v>
-      </c>
-      <c r="N35" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
@@ -8192,7 +8653,7 @@
         <v>1763.83</v>
       </c>
       <c r="E36" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F36">
         <v>38.72</v>
@@ -8204,22 +8665,22 @@
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="J36" t="s">
+        <v>367</v>
+      </c>
+      <c r="K36" t="s">
+        <v>9</v>
+      </c>
+      <c r="L36" t="s">
         <v>368</v>
       </c>
-      <c r="K36" t="s">
-        <v>9</v>
-      </c>
-      <c r="L36" t="s">
-        <v>369</v>
-      </c>
       <c r="M36" t="s">
+        <v>370</v>
+      </c>
+      <c r="N36" t="s">
         <v>371</v>
-      </c>
-      <c r="N36" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
@@ -8236,7 +8697,7 @@
         <v>1454.96</v>
       </c>
       <c r="E37" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F37">
         <v>25.29</v>
@@ -8248,22 +8709,22 @@
         <v>3</v>
       </c>
       <c r="I37" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J37" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="K37" t="s">
         <v>9</v>
       </c>
       <c r="L37" t="s">
+        <v>406</v>
+      </c>
+      <c r="M37" t="s">
         <v>407</v>
       </c>
-      <c r="M37" t="s">
+      <c r="N37" t="s">
         <v>408</v>
-      </c>
-      <c r="N37" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
@@ -8280,7 +8741,7 @@
         <v>1421.43</v>
       </c>
       <c r="E38" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F38">
         <v>24.69</v>
@@ -8292,22 +8753,22 @@
         <v>3</v>
       </c>
       <c r="I38" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J38" t="s">
+        <v>450</v>
+      </c>
+      <c r="K38" t="s">
+        <v>9</v>
+      </c>
+      <c r="L38" t="s">
         <v>451</v>
       </c>
-      <c r="K38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L38" t="s">
+      <c r="M38" t="s">
         <v>452</v>
       </c>
-      <c r="M38" t="s">
+      <c r="N38" t="s">
         <v>453</v>
-      </c>
-      <c r="N38" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
@@ -8324,7 +8785,7 @@
         <v>1498.35</v>
       </c>
       <c r="E39" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F39">
         <v>55.86</v>
@@ -8336,22 +8797,22 @@
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="J39" t="s">
+        <v>472</v>
+      </c>
+      <c r="K39" t="s">
+        <v>9</v>
+      </c>
+      <c r="L39" t="s">
         <v>473</v>
       </c>
-      <c r="K39" t="s">
-        <v>9</v>
-      </c>
-      <c r="L39" t="s">
+      <c r="M39" t="s">
         <v>474</v>
       </c>
-      <c r="M39" t="s">
+      <c r="N39" t="s">
         <v>475</v>
-      </c>
-      <c r="N39" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
@@ -8368,7 +8829,7 @@
         <v>1688.99</v>
       </c>
       <c r="E40" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F40">
         <v>14.71</v>
@@ -8380,22 +8841,22 @@
         <v>0</v>
       </c>
       <c r="I40" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J40" t="s">
+        <v>334</v>
+      </c>
+      <c r="K40" t="s">
+        <v>9</v>
+      </c>
+      <c r="L40" t="s">
         <v>335</v>
       </c>
-      <c r="K40" t="s">
-        <v>9</v>
-      </c>
-      <c r="L40" t="s">
-        <v>336</v>
-      </c>
       <c r="M40" t="s">
+        <v>337</v>
+      </c>
+      <c r="N40" t="s">
         <v>338</v>
-      </c>
-      <c r="N40" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.2">
@@ -8412,7 +8873,7 @@
         <v>1429.73</v>
       </c>
       <c r="E41" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F41">
         <v>-26.2</v>
@@ -8424,22 +8885,22 @@
         <v>2</v>
       </c>
       <c r="I41" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J41" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="K41" t="s">
         <v>2</v>
       </c>
       <c r="L41" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="M41" t="s">
+        <v>365</v>
+      </c>
+      <c r="N41" t="s">
         <v>366</v>
-      </c>
-      <c r="N41" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
@@ -8456,7 +8917,7 @@
         <v>1876.4</v>
       </c>
       <c r="E42" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F42">
         <v>40.42</v>
@@ -8468,7 +8929,7 @@
         <v>2</v>
       </c>
       <c r="I42" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="J42" t="s">
         <v>187</v>
@@ -8500,7 +8961,7 @@
         <v>1514.77</v>
       </c>
       <c r="E43" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F43">
         <v>59.33</v>
@@ -8512,7 +8973,7 @@
         <v>2</v>
       </c>
       <c r="I43" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="J43" t="s">
         <v>11</v>
@@ -8544,7 +9005,7 @@
         <v>1649.4</v>
       </c>
       <c r="E44" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F44">
         <v>46.95</v>
@@ -8556,22 +9017,22 @@
         <v>2</v>
       </c>
       <c r="I44" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="J44" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="K44" t="s">
         <v>9</v>
       </c>
       <c r="L44" t="s">
+        <v>504</v>
+      </c>
+      <c r="M44" t="s">
         <v>505</v>
       </c>
-      <c r="M44" t="s">
+      <c r="N44" t="s">
         <v>506</v>
-      </c>
-      <c r="N44" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.2">
@@ -8588,7 +9049,7 @@
         <v>1483.05</v>
       </c>
       <c r="E45" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F45">
         <v>36.82</v>
@@ -8600,7 +9061,7 @@
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J45" t="s">
         <v>7</v>
@@ -8609,13 +9070,13 @@
         <v>2</v>
       </c>
       <c r="L45" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M45" t="s">
+        <v>327</v>
+      </c>
+      <c r="N45" t="s">
         <v>328</v>
-      </c>
-      <c r="N45" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
@@ -8632,7 +9093,7 @@
         <v>1599.04</v>
       </c>
       <c r="E46" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F46">
         <v>39.93</v>
@@ -8644,22 +9105,22 @@
         <v>3</v>
       </c>
       <c r="I46" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="J46" t="s">
+        <v>307</v>
+      </c>
+      <c r="K46" t="s">
+        <v>9</v>
+      </c>
+      <c r="L46" t="s">
         <v>308</v>
       </c>
-      <c r="K46" t="s">
-        <v>9</v>
-      </c>
-      <c r="L46" t="s">
-        <v>309</v>
-      </c>
       <c r="M46" t="s">
+        <v>310</v>
+      </c>
+      <c r="N46" t="s">
         <v>311</v>
-      </c>
-      <c r="N46" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
@@ -8676,7 +9137,7 @@
         <v>1673.07</v>
       </c>
       <c r="E47" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F47">
         <v>-34.9</v>
@@ -8688,22 +9149,22 @@
         <v>-3</v>
       </c>
       <c r="I47" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="J47" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="K47" t="s">
         <v>2</v>
       </c>
       <c r="L47" t="s">
+        <v>508</v>
+      </c>
+      <c r="M47" t="s">
         <v>509</v>
       </c>
-      <c r="M47" t="s">
+      <c r="N47" t="s">
         <v>510</v>
-      </c>
-      <c r="N47" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
@@ -8720,7 +9181,7 @@
         <v>1673.13</v>
       </c>
       <c r="E48" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F48">
         <v>38.909999999999997</v>
@@ -8732,22 +9193,22 @@
         <v>-4</v>
       </c>
       <c r="I48" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="J48" t="s">
+        <v>280</v>
+      </c>
+      <c r="K48" t="s">
+        <v>9</v>
+      </c>
+      <c r="L48" t="s">
         <v>281</v>
       </c>
-      <c r="K48" t="s">
-        <v>9</v>
-      </c>
-      <c r="L48" t="s">
-        <v>282</v>
-      </c>
       <c r="M48" t="s">
+        <v>283</v>
+      </c>
+      <c r="N48" t="s">
         <v>284</v>
-      </c>
-      <c r="N48" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.2">
@@ -8764,7 +9225,7 @@
         <v>1465.34</v>
       </c>
       <c r="E49" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F49">
         <v>41.3</v>
@@ -8776,7 +9237,7 @@
         <v>5</v>
       </c>
       <c r="I49" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J49" t="s">
         <v>13</v>
@@ -8814,22 +9275,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C1" t="s">
         <v>531</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>532</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>533</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>534</v>
-      </c>
-      <c r="F1" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -8843,13 +9304,13 @@
         <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E2" t="s">
+        <v>295</v>
+      </c>
+      <c r="F2" t="s">
         <v>296</v>
-      </c>
-      <c r="F2" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -8863,13 +9324,13 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E3" t="s">
+        <v>291</v>
+      </c>
+      <c r="F3" t="s">
         <v>292</v>
-      </c>
-      <c r="F3" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -8877,19 +9338,19 @@
         <v>80</v>
       </c>
       <c r="B4" t="s">
+        <v>454</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
         <v>455</v>
       </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>456</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>457</v>
-      </c>
-      <c r="F4" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -8897,19 +9358,19 @@
         <v>125</v>
       </c>
       <c r="B5" t="s">
+        <v>458</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
         <v>459</v>
       </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
-        <v>460</v>
-      </c>
       <c r="E5" t="s">
+        <v>404</v>
+      </c>
+      <c r="F5" t="s">
         <v>405</v>
-      </c>
-      <c r="F5" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -8917,19 +9378,19 @@
         <v>102</v>
       </c>
       <c r="B6" t="s">
+        <v>391</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
         <v>392</v>
       </c>
-      <c r="C6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" t="s">
-        <v>393</v>
-      </c>
       <c r="E6" t="s">
+        <v>394</v>
+      </c>
+      <c r="F6" t="s">
         <v>395</v>
-      </c>
-      <c r="F6" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -8937,19 +9398,19 @@
         <v>67</v>
       </c>
       <c r="B7" t="s">
+        <v>460</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s">
         <v>461</v>
       </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>462</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>463</v>
-      </c>
-      <c r="F7" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -8957,19 +9418,19 @@
         <v>73</v>
       </c>
       <c r="B8" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C8" t="s">
         <v>9</v>
       </c>
       <c r="D8" t="s">
+        <v>464</v>
+      </c>
+      <c r="E8" t="s">
         <v>465</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>466</v>
-      </c>
-      <c r="F8" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -8983,13 +9444,13 @@
         <v>25</v>
       </c>
       <c r="D9" t="s">
+        <v>467</v>
+      </c>
+      <c r="E9" t="s">
         <v>468</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>469</v>
-      </c>
-      <c r="F9" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -8997,19 +9458,19 @@
         <v>111</v>
       </c>
       <c r="B10" t="s">
+        <v>428</v>
+      </c>
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
         <v>429</v>
       </c>
-      <c r="C10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" t="s">
-        <v>430</v>
-      </c>
       <c r="E10" t="s">
+        <v>431</v>
+      </c>
+      <c r="F10" t="s">
         <v>432</v>
-      </c>
-      <c r="F10" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -9103,13 +9564,13 @@
         <v>9</v>
       </c>
       <c r="D15" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E15" t="s">
+        <v>273</v>
+      </c>
+      <c r="F15" t="s">
         <v>274</v>
-      </c>
-      <c r="F15" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
@@ -9137,19 +9598,19 @@
         <v>103</v>
       </c>
       <c r="B17" t="s">
+        <v>414</v>
+      </c>
+      <c r="C17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" t="s">
         <v>415</v>
       </c>
-      <c r="C17" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" t="s">
-        <v>416</v>
-      </c>
       <c r="E17" t="s">
+        <v>417</v>
+      </c>
+      <c r="F17" t="s">
         <v>418</v>
-      </c>
-      <c r="F17" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
@@ -9163,13 +9624,13 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
+        <v>447</v>
+      </c>
+      <c r="E18" t="s">
         <v>448</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>449</v>
-      </c>
-      <c r="F18" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
@@ -9183,13 +9644,13 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
+        <v>476</v>
+      </c>
+      <c r="E19" t="s">
         <v>477</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>478</v>
-      </c>
-      <c r="F19" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
@@ -9197,19 +9658,19 @@
         <v>87</v>
       </c>
       <c r="B20" t="s">
+        <v>443</v>
+      </c>
+      <c r="C20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" t="s">
         <v>444</v>
       </c>
-      <c r="C20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>445</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>446</v>
-      </c>
-      <c r="F20" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
@@ -9223,13 +9684,13 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
+        <v>479</v>
+      </c>
+      <c r="E21" t="s">
         <v>480</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>481</v>
-      </c>
-      <c r="F21" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
@@ -9237,19 +9698,19 @@
         <v>75</v>
       </c>
       <c r="B22" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C22" t="s">
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E22" t="s">
+        <v>342</v>
+      </c>
+      <c r="F22" t="s">
         <v>343</v>
-      </c>
-      <c r="F22" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
@@ -9257,19 +9718,19 @@
         <v>104</v>
       </c>
       <c r="B23" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C23" t="s">
         <v>2</v>
       </c>
       <c r="D23" t="s">
+        <v>483</v>
+      </c>
+      <c r="E23" t="s">
         <v>484</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>485</v>
-      </c>
-      <c r="F23" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
@@ -9297,19 +9758,19 @@
         <v>90</v>
       </c>
       <c r="B25" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C25" t="s">
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E25" t="s">
+        <v>374</v>
+      </c>
+      <c r="F25" t="s">
         <v>375</v>
-      </c>
-      <c r="F25" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
@@ -9317,19 +9778,19 @@
         <v>97</v>
       </c>
       <c r="B26" t="s">
+        <v>486</v>
+      </c>
+      <c r="C26" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" t="s">
         <v>487</v>
       </c>
-      <c r="C26" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>488</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>489</v>
-      </c>
-      <c r="F26" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
@@ -9337,19 +9798,19 @@
         <v>126</v>
       </c>
       <c r="B27" t="s">
+        <v>376</v>
+      </c>
+      <c r="C27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" t="s">
         <v>377</v>
       </c>
-      <c r="C27" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" t="s">
-        <v>378</v>
-      </c>
       <c r="E27" t="s">
+        <v>379</v>
+      </c>
+      <c r="F27" t="s">
         <v>380</v>
-      </c>
-      <c r="F27" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
@@ -9383,13 +9844,13 @@
         <v>2</v>
       </c>
       <c r="D29" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E29" t="s">
+        <v>319</v>
+      </c>
+      <c r="F29" t="s">
         <v>320</v>
-      </c>
-      <c r="F29" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
@@ -9397,19 +9858,19 @@
         <v>74</v>
       </c>
       <c r="B30" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C30" t="s">
         <v>9</v>
       </c>
       <c r="D30" t="s">
+        <v>490</v>
+      </c>
+      <c r="E30" t="s">
         <v>491</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>492</v>
-      </c>
-      <c r="F30" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
@@ -9423,13 +9884,13 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E31" t="s">
+        <v>287</v>
+      </c>
+      <c r="F31" t="s">
         <v>288</v>
-      </c>
-      <c r="F31" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
@@ -9437,19 +9898,19 @@
         <v>105</v>
       </c>
       <c r="B32" t="s">
+        <v>493</v>
+      </c>
+      <c r="C32" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" t="s">
         <v>494</v>
       </c>
-      <c r="C32" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>495</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>496</v>
-      </c>
-      <c r="F32" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
@@ -9477,19 +9938,19 @@
         <v>140</v>
       </c>
       <c r="B34" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C34" t="s">
         <v>25</v>
       </c>
       <c r="D34" t="s">
+        <v>498</v>
+      </c>
+      <c r="E34" t="s">
         <v>499</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>500</v>
-      </c>
-      <c r="F34" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
@@ -9497,19 +9958,19 @@
         <v>79</v>
       </c>
       <c r="B35" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C35" t="s">
         <v>9</v>
       </c>
       <c r="D35" t="s">
+        <v>501</v>
+      </c>
+      <c r="E35" t="s">
         <v>502</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>503</v>
-      </c>
-      <c r="F35" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
@@ -9517,19 +9978,19 @@
         <v>130</v>
       </c>
       <c r="B36" t="s">
+        <v>367</v>
+      </c>
+      <c r="C36" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" t="s">
         <v>368</v>
       </c>
-      <c r="C36" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" t="s">
-        <v>369</v>
-      </c>
       <c r="E36" t="s">
+        <v>370</v>
+      </c>
+      <c r="F36" t="s">
         <v>371</v>
-      </c>
-      <c r="F36" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
@@ -9537,19 +9998,19 @@
         <v>69</v>
       </c>
       <c r="B37" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C37" t="s">
         <v>9</v>
       </c>
       <c r="D37" t="s">
+        <v>406</v>
+      </c>
+      <c r="E37" t="s">
         <v>407</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>408</v>
-      </c>
-      <c r="F37" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
@@ -9557,19 +10018,19 @@
         <v>112</v>
       </c>
       <c r="B38" t="s">
+        <v>450</v>
+      </c>
+      <c r="C38" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" t="s">
         <v>451</v>
       </c>
-      <c r="C38" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>452</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>453</v>
-      </c>
-      <c r="F38" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
@@ -9577,19 +10038,19 @@
         <v>76</v>
       </c>
       <c r="B39" t="s">
+        <v>472</v>
+      </c>
+      <c r="C39" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" t="s">
         <v>473</v>
       </c>
-      <c r="C39" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>474</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>475</v>
-      </c>
-      <c r="F39" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
@@ -9597,19 +10058,19 @@
         <v>117</v>
       </c>
       <c r="B40" t="s">
+        <v>334</v>
+      </c>
+      <c r="C40" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" t="s">
         <v>335</v>
       </c>
-      <c r="C40" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" t="s">
-        <v>336</v>
-      </c>
       <c r="E40" t="s">
+        <v>337</v>
+      </c>
+      <c r="F40" t="s">
         <v>338</v>
-      </c>
-      <c r="F40" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
@@ -9617,19 +10078,19 @@
         <v>56</v>
       </c>
       <c r="B41" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C41" t="s">
         <v>2</v>
       </c>
       <c r="D41" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E41" t="s">
+        <v>365</v>
+      </c>
+      <c r="F41" t="s">
         <v>366</v>
-      </c>
-      <c r="F41" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
@@ -9677,19 +10138,19 @@
         <v>70</v>
       </c>
       <c r="B44" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C44" t="s">
         <v>9</v>
       </c>
       <c r="D44" t="s">
+        <v>504</v>
+      </c>
+      <c r="E44" t="s">
         <v>505</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>506</v>
-      </c>
-      <c r="F44" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
@@ -9703,33 +10164,33 @@
         <v>2</v>
       </c>
       <c r="D45" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E45" t="s">
+        <v>327</v>
+      </c>
+      <c r="F45" t="s">
         <v>328</v>
       </c>
-      <c r="F45" t="s">
-        <v>329</v>
-      </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46" s="4" t="s">
+      <c r="A46" t="s">
         <v>81</v>
       </c>
       <c r="B46" t="s">
+        <v>307</v>
+      </c>
+      <c r="C46" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" t="s">
         <v>308</v>
       </c>
-      <c r="C46" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" t="s">
-        <v>309</v>
-      </c>
       <c r="E46" t="s">
+        <v>310</v>
+      </c>
+      <c r="F46" t="s">
         <v>311</v>
-      </c>
-      <c r="F46" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
@@ -9737,39 +10198,39 @@
         <v>113</v>
       </c>
       <c r="B47" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C47" t="s">
         <v>2</v>
       </c>
       <c r="D47" t="s">
+        <v>508</v>
+      </c>
+      <c r="E47" t="s">
         <v>509</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
         <v>510</v>
       </c>
-      <c r="F47" t="s">
-        <v>511</v>
-      </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A48" s="5" t="s">
+      <c r="A48" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B48" t="s">
+        <v>280</v>
+      </c>
+      <c r="C48" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" t="s">
         <v>281</v>
       </c>
-      <c r="C48" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" t="s">
-        <v>282</v>
-      </c>
       <c r="E48" t="s">
+        <v>283</v>
+      </c>
+      <c r="F48" t="s">
         <v>284</v>
-      </c>
-      <c r="F48" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">

--- a/data_fifa.xlsx
+++ b/data_fifa.xlsx
@@ -253,27 +253,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tableau4" displayName="Tableau4" ref="A1:K17" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A1:K17"/>
-  <tableColumns count="11">
-    <tableColumn id="1" name="city"/>
-    <tableColumn id="2" name="stadium"/>
-    <tableColumn id="3" name="country"/>
-    <tableColumn id="4" name="let"/>
-    <tableColumn id="5" name="long"/>
-    <tableColumn id="6" name="alt_m"/>
-    <tableColumn id="7" name="capacity"/>
-    <tableColumn id="8" name="temp_C_june"/>
-    <tableColumn id="9" name="humidity_%_june"/>
-    <tableColumn id="10" name="time_zone"/>
-    <tableColumn id="11" name="UTC_Offset"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tableau1" displayName="Tableau1" ref="A1:K73" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tableau1" displayName="Tableau1" ref="A1:K73" headerRowCount="1" totalsRowShown="0">
   <sortState ref="A2:K73">
     <sortCondition ref="G1:G73"/>
   </sortState>
@@ -294,34 +274,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Tableau3" displayName="Tableau3" ref="A1:N49" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A1:N49"/>
-  <sortState ref="A2:I49">
-    <sortCondition ref="A1:A49"/>
-  </sortState>
-  <tableColumns count="14">
-    <tableColumn id="1" name="team"/>
-    <tableColumn id="2" name="group"/>
-    <tableColumn id="3" name="rank_fifa"/>
-    <tableColumn id="4" name="points_fifa"/>
-    <tableColumn id="5" name="federation"/>
-    <tableColumn id="6" name="capital_lat"/>
-    <tableColumn id="7" name="capital_long"/>
-    <tableColumn id="8" name="UTC_capital"/>
-    <tableColumn id="9" name="continent"/>
-    <tableColumn id="10" name="city_camp"/>
-    <tableColumn id="11" name="country_camp"/>
-    <tableColumn id="12" name="camp_name"/>
-    <tableColumn id="13" name="camp_lat"/>
-    <tableColumn id="14" name="camp_long"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Tableau2" displayName="Tableau2" ref="A1:F49" headerRowCount="1" totalsRowShown="0">
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tableau2" displayName="Tableau2" ref="A1:F49" headerRowCount="1" totalsRowShown="0">
   <autoFilter ref="A1:F49"/>
   <sortState ref="A2:F49">
     <sortCondition ref="A1:A49"/>
@@ -659,20 +613,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L30"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
-  <cols>
-    <col width="43.5" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="31.83203125" customWidth="1" min="2" max="2"/>
-    <col width="15.6640625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="11.33203125" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="32.33203125" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="14.33203125" customWidth="1" min="8" max="8"/>
-    <col width="17.33203125" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="43.5" bestFit="1" customWidth="1" min="12" max="12"/>
-  </cols>
+  <dimension ref="A1:L17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -730,6 +672,11 @@
           <t>UTC_Offset</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>elevation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -773,6 +720,9 @@
       <c r="K2" t="n">
         <v>-6</v>
       </c>
+      <c r="L2" t="n">
+        <v>2251</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -816,6 +766,9 @@
       <c r="K3" t="n">
         <v>-6</v>
       </c>
+      <c r="L3" t="n">
+        <v>1665</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -859,6 +812,9 @@
       <c r="K4" t="n">
         <v>-6</v>
       </c>
+      <c r="L4" t="n">
+        <v>494</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -902,6 +858,9 @@
       <c r="K5" t="n">
         <v>-5</v>
       </c>
+      <c r="L5" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -945,6 +904,9 @@
       <c r="K6" t="n">
         <v>-5</v>
       </c>
+      <c r="L6" t="n">
+        <v>193</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -988,6 +950,9 @@
       <c r="K7" t="n">
         <v>-5</v>
       </c>
+      <c r="L7" t="n">
+        <v>259</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1031,6 +996,9 @@
       <c r="K8" t="n">
         <v>-4</v>
       </c>
+      <c r="L8" t="n">
+        <v>316</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1074,6 +1042,9 @@
       <c r="K9" t="n">
         <v>-4</v>
       </c>
+      <c r="L9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1117,6 +1088,9 @@
       <c r="K10" t="n">
         <v>-7</v>
       </c>
+      <c r="L10" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1160,6 +1134,9 @@
       <c r="K11" t="n">
         <v>-7</v>
       </c>
+      <c r="L11" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1203,6 +1180,9 @@
       <c r="K12" t="n">
         <v>-7</v>
       </c>
+      <c r="L12" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1246,6 +1226,9 @@
       <c r="K13" t="n">
         <v>-4</v>
       </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1289,6 +1272,9 @@
       <c r="K14" t="n">
         <v>-4</v>
       </c>
+      <c r="L14" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1332,6 +1318,9 @@
       <c r="K15" t="n">
         <v>-4</v>
       </c>
+      <c r="L15" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1375,6 +1364,9 @@
       <c r="K16" t="n">
         <v>-4</v>
       </c>
+      <c r="L16" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1418,60 +1410,12 @@
       <c r="K17" t="n">
         <v>-7</v>
       </c>
-    </row>
-    <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="1" t="n"/>
-      <c r="L19" s="1" t="n"/>
-    </row>
-    <row r="20" ht="19" customHeight="1">
-      <c r="A20" s="1" t="n"/>
-      <c r="L20" s="1" t="n"/>
-    </row>
-    <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="1" t="n"/>
-      <c r="L21" s="1" t="n"/>
-    </row>
-    <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="1" t="n"/>
-      <c r="L22" s="1" t="n"/>
-    </row>
-    <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="1" t="n"/>
-      <c r="L23" s="1" t="n"/>
-    </row>
-    <row r="24" ht="19" customHeight="1">
-      <c r="A24" s="1" t="n"/>
-      <c r="L24" s="1" t="n"/>
-    </row>
-    <row r="25" ht="19" customHeight="1">
-      <c r="A25" s="1" t="n"/>
-      <c r="L25" s="1" t="n"/>
-    </row>
-    <row r="26" ht="19" customHeight="1">
-      <c r="A26" s="1" t="n"/>
-      <c r="L26" s="1" t="n"/>
-    </row>
-    <row r="27" ht="19" customHeight="1">
-      <c r="A27" s="1" t="n"/>
-      <c r="L27" s="1" t="n"/>
-    </row>
-    <row r="28" ht="19" customHeight="1">
-      <c r="A28" s="1" t="n"/>
-      <c r="L28" s="1" t="n"/>
-    </row>
-    <row r="29" ht="19" customHeight="1">
-      <c r="A29" s="1" t="n"/>
-      <c r="L29" s="1" t="n"/>
-    </row>
-    <row r="30" ht="19" customHeight="1">
-      <c r="A30" s="1" t="n"/>
-      <c r="L30" s="1" t="n"/>
+      <c r="L17" t="n">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -8622,16 +8566,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N49"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
-  <cols>
-    <col width="12.33203125" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12.1640625" customWidth="1" min="6" max="6"/>
-    <col width="13.5" customWidth="1" min="7" max="7"/>
-    <col width="13.33203125" customWidth="1" min="8" max="8"/>
-    <col width="11.33203125" customWidth="1" min="9" max="9"/>
-  </cols>
+  <dimension ref="A1:P49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -8704,6 +8640,16 @@
           <t>camp_long</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>camp_elevation</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>camp_avg_temperature</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8756,15 +8702,17 @@
           <t>University of Kansas</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>38.9543</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>-95.2558</t>
-        </is>
+      <c r="M2" t="n">
+        <v>38.9543</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-95.25579999999999</v>
+      </c>
+      <c r="O2" t="n">
+        <v>287</v>
+      </c>
+      <c r="P2" t="n">
+        <v>27.72978070175438</v>
       </c>
     </row>
     <row r="3">
@@ -8818,15 +8766,17 @@
           <t>Sporting KC Training Centre</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>38.9714</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>-94.8113</t>
-        </is>
+      <c r="M3" t="n">
+        <v>38.9714</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-94.8113</v>
+      </c>
+      <c r="O3" t="n">
+        <v>281</v>
+      </c>
+      <c r="P3" t="n">
+        <v>27.33859649122807</v>
       </c>
     </row>
     <row r="4">
@@ -8880,15 +8830,17 @@
           <t>Oakland Roots/Soul Training Facility</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>37.7505</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>-122.1965</t>
-        </is>
+      <c r="M4" t="n">
+        <v>37.7505</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-122.1965</v>
+      </c>
+      <c r="O4" t="n">
+        <v>9</v>
+      </c>
+      <c r="P4" t="n">
+        <v>15.42530701754386</v>
       </c>
     </row>
     <row r="5">
@@ -8942,15 +8894,17 @@
           <t>UC Santa Barbara - Harder Stadium</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>34.4128</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>-119.8455</t>
-        </is>
+      <c r="M5" t="n">
+        <v>34.4128</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-119.8455</v>
+      </c>
+      <c r="O5" t="n">
+        <v>22</v>
+      </c>
+      <c r="P5" t="n">
+        <v>21.64872807017544</v>
       </c>
     </row>
     <row r="6">
@@ -9004,15 +8958,17 @@
           <t>Seattle Sounders FC Performance Centre and Clubhouse</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>47.4995</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>-122.2270</t>
-        </is>
+      <c r="M6" t="n">
+        <v>47.4995</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-122.227</v>
+      </c>
+      <c r="O6" t="n">
+        <v>42</v>
+      </c>
+      <c r="P6" t="n">
+        <v>14.96535087719298</v>
       </c>
     </row>
     <row r="7">
@@ -9066,15 +9022,17 @@
           <t>RSL Stadium</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>40.5829</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>-111.8932</t>
-        </is>
+      <c r="M7" t="n">
+        <v>40.5829</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-111.8932</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1350</v>
+      </c>
+      <c r="P7" t="n">
+        <v>20.81877192982456</v>
       </c>
     </row>
     <row r="8">
@@ -9128,15 +9086,17 @@
           <t>Columbia Park Training Facility</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>40.7920</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>-74.0539</t>
-        </is>
+      <c r="M8" t="n">
+        <v>40.792</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-74.0539</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P8" t="n">
+        <v>22.61214912280701</v>
       </c>
     </row>
     <row r="9">
@@ -9190,15 +9150,17 @@
           <t>National Soccer Development Centre</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>49.2444</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>-123.2510</t>
-        </is>
+      <c r="M9" t="n">
+        <v>49.2444</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-123.251</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>15.60359649122807</v>
       </c>
     </row>
     <row r="10">
@@ -9252,15 +9214,17 @@
           <t>Waters Sportsplex</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>28.0390</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>-82.5200</t>
-        </is>
+      <c r="M10" t="n">
+        <v>28.039</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-82.52</v>
+      </c>
+      <c r="O10" t="n">
+        <v>13</v>
+      </c>
+      <c r="P10" t="n">
+        <v>31.20070175438597</v>
       </c>
     </row>
     <row r="11">
@@ -9314,15 +9278,17 @@
           <t>Academia Atlas FC</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>20.6258</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>-103.3450</t>
-        </is>
+      <c r="M11" t="n">
+        <v>20.6258</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-103.345</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1566</v>
+      </c>
+      <c r="P11" t="n">
+        <v>23.53057017543859</v>
       </c>
     </row>
     <row r="12">
@@ -9376,15 +9342,17 @@
           <t>Episcopal High School</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>38.8080</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>-77.1030</t>
-        </is>
+      <c r="M12" t="n">
+        <v>38.808</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-77.10299999999999</v>
+      </c>
+      <c r="O12" t="n">
+        <v>15</v>
+      </c>
+      <c r="P12" t="n">
+        <v>25.29872807017544</v>
       </c>
     </row>
     <row r="13">
@@ -9438,15 +9406,17 @@
           <t>Florida Atlantic University</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>26.3705</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>-80.1020</t>
-        </is>
+      <c r="M13" t="n">
+        <v>26.3705</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-80.102</v>
+      </c>
+      <c r="O13" t="n">
+        <v>8</v>
+      </c>
+      <c r="P13" t="n">
+        <v>31.06456140350877</v>
       </c>
     </row>
     <row r="14">
@@ -9500,15 +9470,17 @@
           <t>Mansfield Multipurpose Stadium</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>32.5550</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>-97.1440</t>
-        </is>
+      <c r="M14" t="n">
+        <v>32.555</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-97.14400000000001</v>
+      </c>
+      <c r="O14" t="n">
+        <v>200</v>
+      </c>
+      <c r="P14" t="n">
+        <v>31.53666666666667</v>
       </c>
     </row>
     <row r="15">
@@ -9562,15 +9534,17 @@
           <t>Houston Training Centre</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>29.6280</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>-95.3820</t>
-        </is>
+      <c r="M15" t="n">
+        <v>29.628</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-95.38200000000001</v>
+      </c>
+      <c r="O15" t="n">
+        <v>13</v>
+      </c>
+      <c r="P15" t="n">
+        <v>32.90864035087719</v>
       </c>
     </row>
     <row r="16">
@@ -9624,15 +9598,17 @@
           <t>Columbus Crew Performance Centre</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>39.8570</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>-82.9670</t>
-        </is>
+      <c r="M16" t="n">
+        <v>39.857</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-82.967</v>
+      </c>
+      <c r="O16" t="n">
+        <v>225</v>
+      </c>
+      <c r="P16" t="n">
+        <v>23.94311403508772</v>
       </c>
     </row>
     <row r="17">
@@ -9686,15 +9662,17 @@
           <t>Gonzaga University</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>47.6680</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>-117.3985</t>
-        </is>
+      <c r="M17" t="n">
+        <v>47.668</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-117.3985</v>
+      </c>
+      <c r="O17" t="n">
+        <v>584</v>
+      </c>
+      <c r="P17" t="n">
+        <v>16.49184210526316</v>
       </c>
     </row>
     <row r="18">
@@ -9748,15 +9726,17 @@
           <t>Swope Soccer Village</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>39.0247</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>-94.5394</t>
-        </is>
+      <c r="M18" t="n">
+        <v>39.0247</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-94.5394</v>
+      </c>
+      <c r="O18" t="n">
+        <v>281</v>
+      </c>
+      <c r="P18" t="n">
+        <v>27.67254385964912</v>
       </c>
     </row>
     <row r="19">
@@ -9810,15 +9790,17 @@
           <t>Bentley University</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>42.3905</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>-71.2210</t>
-        </is>
+      <c r="M19" t="n">
+        <v>42.3905</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-71.221</v>
+      </c>
+      <c r="O19" t="n">
+        <v>64</v>
+      </c>
+      <c r="P19" t="n">
+        <v>20.81912280701754</v>
       </c>
     </row>
     <row r="20">
@@ -9872,15 +9854,17 @@
           <t>Wake Forest University</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>36.1352</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>-80.2789</t>
-        </is>
+      <c r="M20" t="n">
+        <v>36.1352</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-80.27889999999999</v>
+      </c>
+      <c r="O20" t="n">
+        <v>292</v>
+      </c>
+      <c r="P20" t="n">
+        <v>26.01802631578947</v>
       </c>
     </row>
     <row r="21">
@@ -9934,15 +9918,17 @@
           <t>Bryant University</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>41.9173</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>-71.5350</t>
-        </is>
+      <c r="M21" t="n">
+        <v>41.9173</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-71.535</v>
+      </c>
+      <c r="O21" t="n">
+        <v>126</v>
+      </c>
+      <c r="P21" t="n">
+        <v>20.56043859649123</v>
       </c>
     </row>
     <row r="22">
@@ -9996,15 +9982,17 @@
           <t>Stockton University</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>39.5010</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>-74.5350</t>
-        </is>
+      <c r="M22" t="n">
+        <v>39.501</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-74.535</v>
+      </c>
+      <c r="O22" t="n">
+        <v>25</v>
+      </c>
+      <c r="P22" t="n">
+        <v>23.67236842105263</v>
       </c>
     </row>
     <row r="23">
@@ -10058,15 +10046,17 @@
           <t>Centro Xoloitzcuintle</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>32.4793</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>-116.8789</t>
-        </is>
+      <c r="M23" t="n">
+        <v>32.4793</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-116.8789</v>
+      </c>
+      <c r="O23" t="n">
+        <v>164</v>
+      </c>
+      <c r="P23" t="n">
+        <v>20.03618421052632</v>
       </c>
     </row>
     <row r="24">
@@ -10120,15 +10110,17 @@
           <t>The Greenbrier Sports Performance Centre</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>37.7810</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>-80.2970</t>
-        </is>
+      <c r="M24" t="n">
+        <v>37.781</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-80.297</v>
+      </c>
+      <c r="O24" t="n">
+        <v>663</v>
+      </c>
+      <c r="P24" t="n">
+        <v>20.83815789473684</v>
       </c>
     </row>
     <row r="25">
@@ -10182,15 +10174,17 @@
           <t>Philadelphia Union</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>39.8322</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>-75.3784</t>
-        </is>
+      <c r="M25" t="n">
+        <v>39.8322</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-75.3784</v>
+      </c>
+      <c r="O25" t="n">
+        <v>10</v>
+      </c>
+      <c r="P25" t="n">
+        <v>24.00486842105263</v>
       </c>
     </row>
     <row r="26">
@@ -10244,15 +10238,17 @@
           <t>Nashville SC</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>36.1300</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>-86.7660</t>
-        </is>
+      <c r="M26" t="n">
+        <v>36.13</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-86.76600000000001</v>
+      </c>
+      <c r="O26" t="n">
+        <v>155</v>
+      </c>
+      <c r="P26" t="n">
+        <v>27.67162280701755</v>
       </c>
     </row>
     <row r="27">
@@ -10306,15 +10302,17 @@
           <t>University of Portland</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>45.5720</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>-122.7265</t>
-        </is>
+      <c r="M27" t="n">
+        <v>45.572</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-122.7265</v>
+      </c>
+      <c r="O27" t="n">
+        <v>54</v>
+      </c>
+      <c r="P27" t="n">
+        <v>16.70714912280702</v>
       </c>
     </row>
     <row r="28">
@@ -10368,15 +10366,17 @@
           <t>Chivas Verde Valle</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>20.6830</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>-103.4300</t>
-        </is>
+      <c r="M28" t="n">
+        <v>20.683</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-103.43</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1644</v>
+      </c>
+      <c r="P28" t="n">
+        <v>22.49166666666667</v>
       </c>
     </row>
     <row r="29">
@@ -10430,15 +10430,17 @@
           <t>Centro de Alto Rendimiento (CAR)</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>19.4070</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>-99.0980</t>
-        </is>
+      <c r="M29" t="n">
+        <v>19.407</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-99.098</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2231</v>
+      </c>
+      <c r="P29" t="n">
+        <v>17.85236842105263</v>
       </c>
     </row>
     <row r="30">
@@ -10492,15 +10494,17 @@
           <t>The Pingry School</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>40.6680</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>-74.5810</t>
-        </is>
+      <c r="M30" t="n">
+        <v>40.668</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-74.581</v>
+      </c>
+      <c r="O30" t="n">
+        <v>90</v>
+      </c>
+      <c r="P30" t="n">
+        <v>22.53675438596492</v>
       </c>
     </row>
     <row r="31">
@@ -10554,15 +10558,17 @@
           <t>KC Current Training Facility</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>39.1490</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>-94.6090</t>
-        </is>
+      <c r="M31" t="n">
+        <v>39.149</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-94.60899999999999</v>
+      </c>
+      <c r="O31" t="n">
+        <v>227</v>
+      </c>
+      <c r="P31" t="n">
+        <v>27.63188596491228</v>
       </c>
     </row>
     <row r="32">
@@ -10616,15 +10622,17 @@
           <t>University of San Diego - Torero Stadium</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>32.7700</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>-117.1875</t>
-        </is>
+      <c r="M32" t="n">
+        <v>32.77</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-117.1875</v>
+      </c>
+      <c r="O32" t="n">
+        <v>66</v>
+      </c>
+      <c r="P32" t="n">
+        <v>19.3734649122807</v>
       </c>
     </row>
     <row r="33">
@@ -10678,15 +10686,17 @@
           <t>UNC Greensboro</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>36.0688</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>-79.8080</t>
-        </is>
+      <c r="M33" t="n">
+        <v>36.0688</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-79.80800000000001</v>
+      </c>
+      <c r="O33" t="n">
+        <v>249</v>
+      </c>
+      <c r="P33" t="n">
+        <v>26.04934210526316</v>
       </c>
     </row>
     <row r="34">
@@ -10740,15 +10750,17 @@
           <t>Nottawasaga Training Site</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>44.1430</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>-79.8660</t>
-        </is>
+      <c r="M34" t="n">
+        <v>44.143</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-79.866</v>
+      </c>
+      <c r="O34" t="n">
+        <v>221</v>
+      </c>
+      <c r="P34" t="n">
+        <v>19.19587719298245</v>
       </c>
     </row>
     <row r="35">
@@ -10802,15 +10814,17 @@
           <t>Spartan Soccer Complex</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>37.3460</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>-121.9285</t>
-        </is>
+      <c r="M35" t="n">
+        <v>37.346</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-121.9285</v>
+      </c>
+      <c r="O35" t="n">
+        <v>22</v>
+      </c>
+      <c r="P35" t="n">
+        <v>18.70649122807018</v>
       </c>
     </row>
     <row r="36">
@@ -10864,15 +10878,17 @@
           <t>Gardens North County District Park</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>26.8915</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-80.1350</t>
-        </is>
+      <c r="M36" t="n">
+        <v>26.8915</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-80.13500000000001</v>
+      </c>
+      <c r="O36" t="n">
+        <v>5</v>
+      </c>
+      <c r="P36" t="n">
+        <v>30.87605263157894</v>
       </c>
     </row>
     <row r="37">
@@ -10926,15 +10942,17 @@
           <t>Westmont College</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>34.4427</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>-119.6610</t>
-        </is>
+      <c r="M37" t="n">
+        <v>34.4427</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-119.661</v>
+      </c>
+      <c r="O37" t="n">
+        <v>157</v>
+      </c>
+      <c r="P37" t="n">
+        <v>21.21425438596491</v>
       </c>
     </row>
     <row r="38">
@@ -10988,15 +11006,17 @@
           <t>Austin FC Stadium</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>30.3881</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>-97.7196</t>
-        </is>
+      <c r="M38" t="n">
+        <v>30.3881</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-97.7196</v>
+      </c>
+      <c r="O38" t="n">
+        <v>233</v>
+      </c>
+      <c r="P38" t="n">
+        <v>31.62894736842105</v>
       </c>
     </row>
     <row r="39">
@@ -11050,15 +11070,17 @@
           <t>Charlotte FC</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>35.2253</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>-80.8530</t>
-        </is>
+      <c r="M39" t="n">
+        <v>35.2253</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-80.85299999999999</v>
+      </c>
+      <c r="O39" t="n">
+        <v>220</v>
+      </c>
+      <c r="P39" t="n">
+        <v>26.99122807017544</v>
       </c>
     </row>
     <row r="40">
@@ -11112,15 +11134,17 @@
           <t>Rutgers University</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>40.5240</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>-74.4350</t>
-        </is>
+      <c r="M40" t="n">
+        <v>40.524</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-74.435</v>
+      </c>
+      <c r="O40" t="n">
+        <v>38</v>
+      </c>
+      <c r="P40" t="n">
+        <v>23.13083333333334</v>
       </c>
     </row>
     <row r="41">
@@ -11174,15 +11198,17 @@
           <t>CF Pachuca - Universidad Del Futbol</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>20.0901</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>-98.7536</t>
-        </is>
+      <c r="M41" t="n">
+        <v>20.0901</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-98.75360000000001</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2365</v>
+      </c>
+      <c r="P41" t="n">
+        <v>15.16754385964912</v>
       </c>
     </row>
     <row r="42">
@@ -11236,15 +11262,17 @@
           <t>Baylor School</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>35.0822</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>-85.2980</t>
-        </is>
+      <c r="M42" t="n">
+        <v>35.0822</v>
+      </c>
+      <c r="N42" t="n">
+        <v>-85.298</v>
+      </c>
+      <c r="O42" t="n">
+        <v>270</v>
+      </c>
+      <c r="P42" t="n">
+        <v>26.71934210526316</v>
       </c>
     </row>
     <row r="43">
@@ -11298,15 +11326,17 @@
           <t>FC Dallas Stadium</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>33.1546</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>-96.8350</t>
-        </is>
+      <c r="M43" t="n">
+        <v>33.1546</v>
+      </c>
+      <c r="N43" t="n">
+        <v>-96.83499999999999</v>
+      </c>
+      <c r="O43" t="n">
+        <v>186</v>
+      </c>
+      <c r="P43" t="n">
+        <v>31.31171052631579</v>
       </c>
     </row>
     <row r="44">
@@ -11360,15 +11390,17 @@
           <t>SDJA</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>32.9481</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>-117.2340</t>
-        </is>
+      <c r="M44" t="n">
+        <v>32.9481</v>
+      </c>
+      <c r="N44" t="n">
+        <v>-117.234</v>
+      </c>
+      <c r="O44" t="n">
+        <v>66</v>
+      </c>
+      <c r="P44" t="n">
+        <v>19.70504385964912</v>
       </c>
     </row>
     <row r="45">
@@ -11422,15 +11454,17 @@
           <t>Rayados Training Centre</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>25.7220</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>-100.2470</t>
-        </is>
+      <c r="M45" t="n">
+        <v>25.722</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-100.247</v>
+      </c>
+      <c r="O45" t="n">
+        <v>479</v>
+      </c>
+      <c r="P45" t="n">
+        <v>30.49228070175438</v>
       </c>
     </row>
     <row r="46">
@@ -11484,15 +11518,17 @@
           <t>Arizona Athletic Grounds</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>33.3550</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>-111.6830</t>
-        </is>
+      <c r="M46" t="n">
+        <v>33.355</v>
+      </c>
+      <c r="N46" t="n">
+        <v>-111.683</v>
+      </c>
+      <c r="O46" t="n">
+        <v>405</v>
+      </c>
+      <c r="P46" t="n">
+        <v>31.62574561403509</v>
       </c>
     </row>
     <row r="47">
@@ -11546,15 +11582,17 @@
           <t>Mayakoba Training Centre Cancun</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>20.7010</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>-87.0240</t>
-        </is>
+      <c r="M47" t="n">
+        <v>20.701</v>
+      </c>
+      <c r="N47" t="n">
+        <v>-87.024</v>
+      </c>
+      <c r="O47" t="n">
+        <v>14</v>
+      </c>
+      <c r="P47" t="n">
+        <v>31.97087719298246</v>
       </c>
     </row>
     <row r="48">
@@ -11608,15 +11646,17 @@
           <t>Great Park Sports Complex</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>33.6713</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>-117.7410</t>
-        </is>
+      <c r="M48" t="n">
+        <v>33.6713</v>
+      </c>
+      <c r="N48" t="n">
+        <v>-117.741</v>
+      </c>
+      <c r="O48" t="n">
+        <v>82</v>
+      </c>
+      <c r="P48" t="n">
+        <v>20.01982456140351</v>
       </c>
     </row>
     <row r="49">
@@ -11670,22 +11710,21 @@
           <t>Atlanta United Training Centre</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>33.9690</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>-84.5720</t>
-        </is>
+      <c r="M49" t="n">
+        <v>33.969</v>
+      </c>
+      <c r="N49" t="n">
+        <v>-84.572</v>
+      </c>
+      <c r="O49" t="n">
+        <v>338</v>
+      </c>
+      <c r="P49" t="n">
+        <v>26.88627192982456</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
